--- a/px-files/sitemaps/sitemap.xlsx
+++ b/px-files/sitemaps/sitemap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomk79/mydoc_TomK/projs/pickles2/tomk79/preset-pickles2-clover/px-files/sitemaps/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomk79/mydoc_TomK/projs/pickles2/pickles2/pickles2/px-files/sitemaps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C233B0-7F1C-8345-8695-895BF65E0C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156EFBCB-10C5-8A4A-9F51-A38220A01D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sitemap" sheetId="1" r:id="rId1"/>
@@ -22,10 +22,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
-    <t>row_definition=8&amp;row_data_start=9&amp;skip_empty_col=20&amp;version=2.0.8</t>
-  </si>
-  <si>
-    <t>Exported: 2017-12-16 17:21:55</t>
+    <t>row_definition=8&amp;row_data_start=9&amp;skip_empty_col=20&amp;version=2.3.3</t>
+  </si>
+  <si>
+    <t>[Pickles 2] Sitemap</t>
+  </si>
+  <si>
+    <t>Exported: 2025-07-16 23:46:38</t>
   </si>
   <si>
     <t>ページID</t>
@@ -52,6 +55,9 @@
     <t>コンテンツファイルの格納先</t>
   </si>
   <si>
+    <t>論理構造上のパス</t>
+  </si>
+  <si>
     <t>一覧表示フラグ</t>
   </si>
   <si>
@@ -76,9 +82,6 @@
     <t>コンテンツの処理方法</t>
   </si>
   <si>
-    <t>削除フラグ</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>content</t>
   </si>
   <si>
+    <t>logical_path</t>
+  </si>
+  <si>
     <t>list_flg</t>
   </si>
   <si>
@@ -127,50 +133,35 @@
     <t>proc_type</t>
   </si>
   <si>
-    <t>**delete_flg</t>
-  </si>
-  <si>
     <t>ホーム</t>
   </si>
   <si>
     <t>/</t>
   </si>
   <si>
+    <t>top</t>
+  </si>
+  <si>
+    <t>このブログについて</t>
+  </si>
+  <si>
+    <t>/about/</t>
+  </si>
+  <si>
+    <t>記事一覧</t>
+  </si>
+  <si>
+    <t>/articles/{*}</t>
+  </si>
+  <si>
     <t>EndOfData</t>
-  </si>
-  <si>
-    <t>記事一覧</t>
-    <rPh sb="0" eb="4">
-      <t xml:space="preserve">キジイチラｎ </t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>/articles/{*}</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>このブログについて</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>/about/</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>サイトマップ</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>top</t>
-    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -180,41 +171,30 @@
       <sz val="8"/>
       <color rgb="FF333333"/>
       <name val="メイリオ"/>
-      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="メイリオ"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="メイリオ"/>
-      <family val="2"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="メイリオ"/>
-      <family val="2"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Source Han Sans JP"/>
+      <name val="Ryo Gothic PlusN L"/>
       <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="メイリオ"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color rgb="FF000000"/>
-      <name val="メイリオ"/>
-      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -322,21 +302,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -644,15 +621,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="6" width="3" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="11" width="2" customWidth="1"/>
-    <col min="12" max="12" width="40" customWidth="1"/>
-    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="2" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="10" width="2" customWidth="1"/>
+    <col min="11" max="11" width="40" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
     <col min="14" max="14" width="3" customWidth="1"/>
     <col min="15" max="15" width="9" customWidth="1"/>
     <col min="16" max="16" width="3" customWidth="1"/>
@@ -660,7 +637,7 @@
     <col min="19" max="19" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="10" customHeight="1">
+    <row r="1" spans="1:21" ht="10" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -684,263 +661,255 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="38">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:21" ht="38">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="4"/>
+      <c r="B9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4">
+        <v>1</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="4"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4">
+        <v>1</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="4">
+        <v>1</v>
+      </c>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="4"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4" t="s">
         <v>43</v>
       </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4">
+        <v>1</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="4">
+        <v>1</v>
+      </c>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
     </row>
-    <row r="4" spans="1:22">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="3"/>
-      <c r="B9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3">
-        <v>1</v>
-      </c>
-      <c r="O9" s="11" t="s">
+    <row r="14" spans="1:21" ht="5" customHeight="1">
+      <c r="A14" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="13"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13">
-        <v>1</v>
-      </c>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="13">
-        <v>1</v>
-      </c>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" s="3"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3">
-        <v>1</v>
-      </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="3">
-        <v>1</v>
-      </c>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-    </row>
-    <row r="14" spans="1:22" ht="5" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="2">
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
